--- a/results/link-prediction-gcn/Link/1shot/Wisconsin/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/1shot/Wisconsin/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4167±0.0000</t>
+          <t>0.5278±0.0393</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.4792±0.0295</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.4861±0.0354</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0520</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0170</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0196</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0260</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.6111±0.0098</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.6111±0.0098</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.6111±0.0098</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.4375±0.0000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4375±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0597</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0295</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.3750±0.0000</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.5069±0.0098</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.6181±0.0687</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.5417±0.0510</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5972±0.0428</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5764±0.0260</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.5069±0.0098</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.6042±0.0340</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.6042±0.0340</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.6042±0.0340</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.5278±0.0393</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.5625±0.0613</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.6319±0.0547</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5764±0.0597</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4444±0.0786</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5625±0.0450</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5764±0.0196</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5069±0.0260</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5625±0.0741</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.4931±0.0260</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5903±0.0393</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5903±0.0393</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5903±0.0393</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.5486±0.0547</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.5833±0.1035</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5556±0.0644</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5000±0.1021</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.6042±0.0450</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5833±0.0450</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5486±0.0520</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.6528±0.0196</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5833±0.0450</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.6944±0.0260</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.6181±0.0393</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.6181±0.0393</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.6181±0.0393</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.7708±0.0000</t>
+          <t>0.6597±0.0687</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.4583±0.0000</t>
+          <t>0.6458±0.0170</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6319±0.0354</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4792±0.0000</t>
+          <t>0.4722±0.0393</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4444±0.0786</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.4167±0.0000</t>
+          <t>0.5347±0.0098</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.4583±0.0000</t>
+          <t>0.5069±0.0428</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5000±0.0170</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.5625±0.0780</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.4792±0.0295</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5486±0.0491</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5486±0.0491</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5486±0.0491</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.5069±0.0098</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6181±0.0708</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.5486±0.0393</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4583±0.0589</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4792±0.0295</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.5417±0.0170</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.4792±0.0000</t>
+          <t>0.5625±0.0340</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5347±0.0428</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5278±0.0547</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.4792±0.0295</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5417±0.0295</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5417±0.0295</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5417±0.0295</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6042±0.0613</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.4792±0.0000</t>
+          <t>0.5833±0.0780</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4931±0.0098</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5972±0.0708</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5208±0.0510</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5486±0.0260</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5278±0.0428</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5764±0.0597</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6250±0.0884</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5625±0.0170</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5625±0.0170</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5625±0.0170</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5903±0.0839</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6111±0.0644</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5625±0.0170</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.1250±0.0000</t>
+          <t>0.5556±0.1288</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6434±0.0328</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.5424±0.0000</t>
+          <t>0.6283±0.0340</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.5574±0.0000</t>
+          <t>0.6571±0.0302</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6832±0.0166</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6894±0.0123</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.6795±0.0121</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.7009±0.0162</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.7009±0.0162</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.7009±0.0162</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.7164±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.7164±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.7164±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.6765±0.0000</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6567±0.0000</t>
+          <t>0.6566±0.0143</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.7059±0.0000</t>
+          <t>0.6803±0.0051</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.2105±0.0000</t>
+          <t>0.2222±0.3143</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.7143±0.0000</t>
+          <t>0.6521±0.0206</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.6349±0.0000</t>
+          <t>0.6873±0.0452</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.6866±0.0000</t>
+          <t>0.6413±0.0402</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6918±0.0145</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.7164±0.0000</t>
+          <t>0.6773±0.0006</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.7059±0.0000</t>
+          <t>0.6633±0.0121</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.7168±0.0175</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.7168±0.0175</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.7168±0.0175</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.7000±0.0000</t>
+          <t>0.6736±0.0170</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.6792±0.0000</t>
+          <t>0.6004±0.0199</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.6970±0.0000</t>
+          <t>0.7177±0.0298</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0000±0.0000</t>
+          <t>0.2569±0.1990</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6111±0.0786</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.6567±0.0000</t>
+          <t>0.6505±0.0634</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6966±0.0087</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6668±0.0154</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6976±0.0373</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.6351±0.0235</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6651±0.0426</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6651±0.0426</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6651±0.0426</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.6957±0.0000</t>
+          <t>0.6840±0.0258</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.7059±0.0000</t>
+          <t>0.7021±0.0437</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6733±0.0440</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.3229±0.2315</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.6962±0.0202</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.6415±0.0000</t>
+          <t>0.6576±0.0455</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.6545±0.0000</t>
+          <t>0.6294±0.0178</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.6230±0.0000</t>
+          <t>0.7191±0.0040</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.6452±0.0000</t>
+          <t>0.6807±0.0361</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.7097±0.0000</t>
+          <t>0.7663±0.0154</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.7368±0.0000</t>
+          <t>0.6817±0.0213</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.7368±0.0000</t>
+          <t>0.6817±0.0213</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.7368±0.0000</t>
+          <t>0.6817±0.0213</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.8136±0.0000</t>
+          <t>0.7424±0.0429</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.5517±0.0000</t>
+          <t>0.6902±0.0194</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.7037±0.0000</t>
+          <t>0.7039±0.0208</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.6479±0.0000</t>
+          <t>0.6111±0.0786</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6057±0.0862</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.5758±0.0000</t>
+          <t>0.6520±0.0181</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.5938±0.0000</t>
+          <t>0.6400±0.0525</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6537±0.0120</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.6815±0.0450</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.7059±0.0000</t>
+          <t>0.6434±0.0328</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.7164±0.0000</t>
+          <t>0.6704±0.0311</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.7164±0.0000</t>
+          <t>0.6704±0.0311</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.7164±0.0000</t>
+          <t>0.6704±0.0311</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.7273±0.0000</t>
+          <t>0.6633±0.0047</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.7143±0.0000</t>
+          <t>0.7098±0.0480</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.7302±0.0000</t>
+          <t>0.6835±0.0105</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0.0000±0.0000</t>
+          <t>0.5146±0.2150</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6473±0.0273</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.6970±0.0000</t>
+          <t>0.6796±0.0120</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.5098±0.0000</t>
+          <t>0.6869±0.0144</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6467±0.0500</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.6765±0.0000</t>
+          <t>0.6671±0.0330</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.6473±0.0273</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6630±0.0125</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6630±0.0125</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6630±0.0125</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.6866±0.0000</t>
+          <t>0.6761±0.0078</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.7002±0.0209</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.6479±0.0000</t>
+          <t>0.7050±0.0410</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0000±0.0000</t>
+          <t>0.3983±0.2873</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6966±0.0276</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6102±0.0000</t>
+          <t>0.6381±0.0440</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6333±0.0000</t>
+          <t>0.6587±0.0183</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6637±0.0184</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6797±0.0185</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.7302±0.0449</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6799±0.0173</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6799±0.0173</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6799±0.0173</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.7068±0.0369</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.7001±0.0243</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6800±0.0040</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.2865±0.0000</t>
+          <t>0.5920±0.1339</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.5972±0.0981</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5339±0.0000</t>
+          <t>0.4925±0.0220</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.4531±0.0000</t>
+          <t>0.6508±0.0466</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6832±0.0000</t>
+          <t>0.7176±0.0993</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.6207±0.0000</t>
+          <t>0.7422±0.0579</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6372±0.0000</t>
+          <t>0.7124±0.0893</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7847±0.0000</t>
+          <t>0.7821±0.0358</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7847±0.0000</t>
+          <t>0.7821±0.0358</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7847±0.0000</t>
+          <t>0.7821±0.0358</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.8542±0.0000</t>
+          <t>0.7054±0.0509</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.5590±0.0000</t>
+          <t>0.6007±0.0504</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.6597±0.0000</t>
+          <t>0.6259±0.0480</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.3351±0.0000</t>
+          <t>0.6042±0.0763</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7674±0.0000</t>
+          <t>0.6505±0.0501</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.6311±0.0000</t>
+          <t>0.6389±0.0933</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6354±0.0000</t>
+          <t>0.5854±0.0626</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.7054±0.0319</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.7274±0.0000</t>
+          <t>0.7477±0.0466</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.8186±0.0000</t>
+          <t>0.7159±0.0496</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6884±0.0000</t>
+          <t>0.6965±0.0778</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6884±0.0000</t>
+          <t>0.6965±0.0778</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6884±0.0000</t>
+          <t>0.6965±0.0778</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.7569±0.0000</t>
+          <t>0.7604±0.0796</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7326±0.0000</t>
+          <t>0.6360±0.0745</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.6198±0.0000</t>
+          <t>0.7205±0.0521</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.4514±0.0000</t>
+          <t>0.5133±0.1793</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.7882±0.0000</t>
+          <t>0.5735±0.0766</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6224±0.0000</t>
+          <t>0.6076±0.0792</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.6264±0.0672</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.7517±0.0000</t>
+          <t>0.6950±0.1352</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.7743±0.0000</t>
+          <t>0.7674±0.0161</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.7865±0.0000</t>
+          <t>0.6233±0.0293</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7535±0.0000</t>
+          <t>0.6583±0.0494</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7535±0.0000</t>
+          <t>0.6583±0.0494</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7535±0.0000</t>
+          <t>0.6583±0.0494</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.8247±0.0000</t>
+          <t>0.7338±0.0824</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.6684±0.0000</t>
+          <t>0.7170±0.0472</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7665±0.0000</t>
+          <t>0.7066±0.0797</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.5243±0.0000</t>
+          <t>0.4572±0.1498</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7500±0.0000</t>
+          <t>0.7616±0.0759</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5966±0.0359</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5469±0.0518</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.6701±0.0320</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.6887±0.0904</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.6892±0.0000</t>
+          <t>0.7980±0.0673</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.6849±0.0000</t>
+          <t>0.6372±0.0509</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.6849±0.0000</t>
+          <t>0.6372±0.0509</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.6849±0.0000</t>
+          <t>0.6372±0.0509</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.7378±0.0000</t>
+          <t>0.7711±0.0440</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.5955±0.0000</t>
+          <t>0.7355±0.0616</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6563±0.0592</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.4861±0.0000</t>
+          <t>0.5162±0.1312</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.7899±0.0000</t>
+          <t>0.6105±0.1143</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5243±0.0000</t>
+          <t>0.5868±0.0542</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.5799±0.0000</t>
+          <t>0.6157±0.1568</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.7743±0.0000</t>
+          <t>0.6988±0.0796</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.7292±0.0000</t>
+          <t>0.7106±0.0486</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.8108±0.0000</t>
+          <t>0.6649±0.0865</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.7569±0.0000</t>
+          <t>0.7694±0.0362</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.7569±0.0000</t>
+          <t>0.7694±0.0362</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.7569±0.0000</t>
+          <t>0.7694±0.0362</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.8455±0.0000</t>
+          <t>0.7321±0.0345</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7743±0.0000</t>
+          <t>0.7407±0.0623</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.7951±0.0000</t>
+          <t>0.7946±0.0323</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.2865±0.0000</t>
+          <t>0.4994±0.1637</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.7708±0.0000</t>
+          <t>0.5880±0.1077</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6476±0.0381</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.4609±0.0000</t>
+          <t>0.6062±0.0187</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.6409±0.1088</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.7726±0.0000</t>
+          <t>0.7442±0.0181</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.8194±0.0000</t>
+          <t>0.6458±0.0276</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.7517±0.0000</t>
+          <t>0.6979±0.0507</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.7517±0.0000</t>
+          <t>0.6979±0.0507</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.7517±0.0000</t>
+          <t>0.6979±0.0507</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.8003±0.0000</t>
+          <t>0.7992±0.0503</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.7760±0.0528</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.7274±0.0000</t>
+          <t>0.7708±0.0357</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.2691±0.0000</t>
+          <t>0.5550±0.1340</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.6050±0.0000</t>
+          <t>0.7263±0.0429</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.5747±0.0000</t>
+          <t>0.5310±0.0405</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.6354±0.0000</t>
+          <t>0.6143±0.0350</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.7274±0.0000</t>
+          <t>0.6534±0.0583</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.7431±0.0000</t>
+          <t>0.7280±0.0447</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7483±0.0000</t>
+          <t>0.7135±0.0752</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7135±0.0000</t>
+          <t>0.7477±0.0989</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7135±0.0000</t>
+          <t>0.7477±0.0989</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7135±0.0000</t>
+          <t>0.7477±0.0989</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.6979±0.0000</t>
+          <t>0.7410±0.0489</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.6701±0.0000</t>
+          <t>0.7454±0.0737</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6997±0.0000</t>
+          <t>0.7066±0.0668</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.4360±0.0000</t>
+          <t>0.6505±0.0959</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6646±0.0000</t>
+          <t>0.6922±0.0707</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5524±0.0000</t>
+          <t>0.4981±0.0105</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.4712±0.0000</t>
+          <t>0.6142±0.0398</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6389±0.0000</t>
+          <t>0.7369±0.0731</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.5754±0.0000</t>
+          <t>0.7508±0.0425</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6766±0.0000</t>
+          <t>0.7549±0.0572</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7941±0.0486</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7941±0.0486</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7215±0.0000</t>
+          <t>0.7941±0.0486</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.8698±0.0000</t>
+          <t>0.7345±0.0316</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.6092±0.0000</t>
+          <t>0.6265±0.0434</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.5929±0.0000</t>
+          <t>0.6344±0.0686</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.4733±0.0000</t>
+          <t>0.6383±0.0734</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7668±0.0000</t>
+          <t>0.7051±0.0535</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6159±0.0000</t>
+          <t>0.6170±0.0895</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5968±0.0000</t>
+          <t>0.5718±0.0648</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6104±0.0000</t>
+          <t>0.6663±0.0362</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6475±0.0000</t>
+          <t>0.7836±0.0723</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.8012±0.0000</t>
+          <t>0.7788±0.0281</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6274±0.0000</t>
+          <t>0.6436±0.0858</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6274±0.0000</t>
+          <t>0.6436±0.0858</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6274±0.0000</t>
+          <t>0.6436±0.0858</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7551±0.0000</t>
+          <t>0.7962±0.0766</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7923±0.0000</t>
+          <t>0.6915±0.0632</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.5719±0.0000</t>
+          <t>0.6867±0.0695</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.5598±0.0000</t>
+          <t>0.6151±0.1342</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.8054±0.0000</t>
+          <t>0.6790±0.0459</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5869±0.0000</t>
+          <t>0.5792±0.0506</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5803±0.0000</t>
+          <t>0.5719±0.0514</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7015±0.0000</t>
+          <t>0.7302±0.1252</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.7405±0.0000</t>
+          <t>0.7576±0.0615</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.7890±0.0000</t>
+          <t>0.6906±0.0364</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.7000±0.0000</t>
+          <t>0.6743±0.0642</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.7000±0.0000</t>
+          <t>0.6743±0.0642</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.7000±0.0000</t>
+          <t>0.6743±0.0642</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.8213±0.0000</t>
+          <t>0.7761±0.0609</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.7275±0.0000</t>
+          <t>0.7343±0.0151</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.7533±0.0000</t>
+          <t>0.7449±0.0559</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.5970±0.0000</t>
+          <t>0.5358±0.1343</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7959±0.0000</t>
+          <t>0.7813±0.0890</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5611±0.0000</t>
+          <t>0.5659±0.0220</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5605±0.0000</t>
+          <t>0.5295±0.0306</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5107±0.0000</t>
+          <t>0.6078±0.0264</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.5219±0.0000</t>
+          <t>0.6563±0.0972</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.6215±0.0000</t>
+          <t>0.7752±0.0903</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.6193±0.0000</t>
+          <t>0.5868±0.0356</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.6193±0.0000</t>
+          <t>0.5868±0.0356</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.6193±0.0000</t>
+          <t>0.5868±0.0356</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6517±0.0000</t>
+          <t>0.7662±0.0487</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.6471±0.0000</t>
+          <t>0.7448±0.0827</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.6056±0.0000</t>
+          <t>0.6147±0.0591</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.5736±0.0000</t>
+          <t>0.5833±0.1343</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.6967±0.0699</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5136±0.0000</t>
+          <t>0.5653±0.0429</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.5785±0.0000</t>
+          <t>0.6191±0.1480</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7076±0.0000</t>
+          <t>0.6754±0.0851</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7242±0.0000</t>
+          <t>0.7220±0.0847</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7918±0.0000</t>
+          <t>0.7200±0.0650</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6963±0.0000</t>
+          <t>0.7979±0.0261</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6963±0.0000</t>
+          <t>0.7979±0.0261</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6963±0.0000</t>
+          <t>0.7979±0.0261</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.8638±0.0000</t>
+          <t>0.7749±0.0179</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8180±0.0000</t>
+          <t>0.7919±0.0267</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7520±0.0000</t>
+          <t>0.7865±0.0365</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.4465±0.0000</t>
+          <t>0.5858±0.1647</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7898±0.0000</t>
+          <t>0.6764±0.0792</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6047±0.0000</t>
+          <t>0.5950±0.0309</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.5034±0.0000</t>
+          <t>0.5624±0.0016</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.6445±0.0968</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8078±0.0000</t>
+          <t>0.7919±0.0093</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.8320±0.0000</t>
+          <t>0.7163±0.0321</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7731±0.0000</t>
+          <t>0.7274±0.0224</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7731±0.0000</t>
+          <t>0.7274±0.0224</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7731±0.0000</t>
+          <t>0.7274±0.0224</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.8190±0.0000</t>
+          <t>0.8293±0.0630</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7440±0.0000</t>
+          <t>0.8076±0.0668</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7154±0.0000</t>
+          <t>0.7255±0.0320</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.3809±0.0000</t>
+          <t>0.6529±0.0946</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.7248±0.0620</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5698±0.0000</t>
+          <t>0.5332±0.0146</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.6884±0.0000</t>
+          <t>0.5886±0.0431</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.7610±0.0000</t>
+          <t>0.7165±0.0267</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.7245±0.0000</t>
+          <t>0.7760±0.0382</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7708±0.0000</t>
+          <t>0.7447±0.0397</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7397±0.0000</t>
+          <t>0.7836±0.0890</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7397±0.0000</t>
+          <t>0.7836±0.0890</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7397±0.0000</t>
+          <t>0.7836±0.0890</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7402±0.0000</t>
+          <t>0.7412±0.0601</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7049±0.0000</t>
+          <t>0.7717±0.0831</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7221±0.0000</t>
+          <t>0.6820±0.0687</t>
         </is>
       </c>
     </row>
